--- a/data/trans_orig/IP07C01-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07C01-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse bien y en forma en 2007 (tasa de respuesta: 89,89%)</t>
+          <t>Menores según la frecuencia de sentirse bien y en forma en 2007 (tasa de respuesta: 89,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51237</t>
+          <t>51270</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>67917</t>
+          <t>68543</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>61,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>53371</t>
+          <t>53212</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>71203</t>
+          <t>71211</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>109758</t>
+          <t>107902</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>132850</t>
+          <t>133238</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>56,5%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36165</t>
+          <t>35580</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52646</t>
+          <t>53055</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46654</t>
+          <t>46280</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64963</t>
+          <t>64226</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>88002</t>
+          <t>88217</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>112287</t>
+          <t>113193</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>48,0%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4016</t>
+          <t>4156</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12634</t>
+          <t>12294</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1858</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8426</t>
+          <t>7991</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6772</t>
+          <t>7248</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17248</t>
+          <t>17948</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2659</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>696</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6290</t>
+          <t>6068</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1154</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7251</t>
+          <t>6940</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>85510</t>
+          <t>84400</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>105655</t>
+          <t>105542</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>92173</t>
+          <t>92710</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>113469</t>
+          <t>113980</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>61,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>183290</t>
+          <t>182168</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>212298</t>
+          <t>214429</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>49,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>58,82%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>65179</t>
+          <t>64942</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>86038</t>
+          <t>85519</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>64994</t>
+          <t>65149</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>86002</t>
+          <t>85603</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>136498</t>
+          <t>135145</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>165897</t>
+          <t>165942</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>45,52%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3756</t>
+          <t>3515</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12509</t>
+          <t>11837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3199</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11178</t>
+          <t>11168</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8214</t>
+          <t>8098</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>19767</t>
+          <t>19362</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>464</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4791</t>
+          <t>5097</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4604</t>
+          <t>4561</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1156</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>6711</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>141559</t>
+          <t>141139</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>168342</t>
+          <t>168791</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>58,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>151488</t>
+          <t>149338</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>179533</t>
+          <t>178687</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>48,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>299468</t>
+          <t>299389</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>337717</t>
+          <t>337005</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>56,13%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>105827</t>
+          <t>105877</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>133162</t>
+          <t>132311</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>117059</t>
+          <t>117657</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>145176</t>
+          <t>145744</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>231239</t>
+          <t>231946</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>269357</t>
+          <t>270952</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>45,13%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9426</t>
+          <t>9331</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>21907</t>
+          <t>21758</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5811</t>
+          <t>5778</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16044</t>
+          <t>15230</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>17829</t>
+          <t>17741</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>32716</t>
+          <t>33339</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>627</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5920</t>
+          <t>5294</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>1380</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8198</t>
+          <t>7878</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2944</t>
+          <t>3074</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11093</t>
+          <t>11059</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -2814,7 +2814,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse bien y en forma en 2012 (tasa de respuesta: 95,62%)</t>
+          <t>Menores según la frecuencia de sentirse bien y en forma en 2012 (tasa de respuesta: 95,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>50654</t>
+          <t>50143</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>70266</t>
+          <t>69734</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>58969</t>
+          <t>58903</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>78962</t>
+          <t>79348</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>114795</t>
+          <t>116270</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>142696</t>
+          <t>143746</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>47,17%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70353</t>
+          <t>70870</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>89634</t>
+          <t>90609</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>47,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>60,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>68334</t>
+          <t>68073</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>88825</t>
+          <t>88314</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>143840</t>
+          <t>144355</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>173463</t>
+          <t>173206</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>47,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>56,84%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4065</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13518</t>
+          <t>12614</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2536</t>
+          <t>2619</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11510</t>
+          <t>12134</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8059</t>
+          <t>8337</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20780</t>
+          <t>21514</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>425</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5188</t>
+          <t>4878</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>565</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5845</t>
+          <t>5553</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1453</t>
+          <t>1606</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8602</t>
+          <t>8434</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43937</t>
+          <t>43926</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64628</t>
+          <t>64535</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>66926</t>
+          <t>65750</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>87805</t>
+          <t>87381</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>116252</t>
+          <t>115177</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>145741</t>
+          <t>144269</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,34%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>82339</t>
+          <t>82867</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>103533</t>
+          <t>103547</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>69627</t>
+          <t>68629</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>90183</t>
+          <t>91406</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>53,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>157504</t>
+          <t>157947</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>186626</t>
+          <t>187872</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>56,44%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6169</t>
+          <t>5858</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17597</t>
+          <t>17149</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4670</t>
+          <t>4787</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13907</t>
+          <t>13909</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>12869</t>
+          <t>13174</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>27072</t>
+          <t>27261</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1407</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8036</t>
+          <t>8123</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2120</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10311</t>
+          <t>9872</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4479</t>
+          <t>4431</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14871</t>
+          <t>14537</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>3360</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4440</t>
+          <t>4554</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>602</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5278</t>
+          <t>5226</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>99565</t>
+          <t>100129</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>126920</t>
+          <t>127878</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>41,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>132059</t>
+          <t>130598</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>161455</t>
+          <t>160436</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>241060</t>
+          <t>238525</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>282589</t>
+          <t>282153</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>44,25%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>158798</t>
+          <t>157383</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>187618</t>
+          <t>185398</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>142485</t>
+          <t>143224</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>171804</t>
+          <t>172721</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>308749</t>
+          <t>309644</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>351898</t>
+          <t>352533</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,19%</t>
+          <t>55,29%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12092</t>
+          <t>11677</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26086</t>
+          <t>25980</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9499</t>
+          <t>9141</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22097</t>
+          <t>22069</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>24152</t>
+          <t>23902</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>44609</t>
+          <t>42202</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,62%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t>2352</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>10689</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3514</t>
+          <t>3444</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12772</t>
+          <t>12100</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7433</t>
+          <t>7287</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19930</t>
+          <t>18687</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3388</t>
+          <t>2740</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4865,7 +4865,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4513</t>
+          <t>5096</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>605</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5493</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5090,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse bien y en forma en 2016 (tasa de respuesta: 95,77%)</t>
+          <t>Menores según la frecuencia de sentirse bien y en forma en 2016 (tasa de respuesta: 95,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5285,12 +5285,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>94674</t>
+          <t>95134</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>115576</t>
+          <t>116531</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5300,12 +5300,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>64,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5320,12 +5320,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>90880</t>
+          <t>91168</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>113490</t>
+          <t>112558</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5335,12 +5335,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>63,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>192124</t>
+          <t>192867</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>223019</t>
+          <t>222821</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5370,12 +5370,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>61,98%</t>
         </is>
       </c>
     </row>
@@ -5398,12 +5398,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>58657</t>
+          <t>58381</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>78742</t>
+          <t>78879</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5413,12 +5413,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5433,12 +5433,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53029</t>
+          <t>54397</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>75993</t>
+          <t>75619</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5448,12 +5448,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5468,12 +5468,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>118106</t>
+          <t>118327</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>148771</t>
+          <t>148111</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5483,12 +5483,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,2%</t>
         </is>
       </c>
     </row>
@@ -5511,12 +5511,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2556</t>
+          <t>2333</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11595</t>
+          <t>10673</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5526,12 +5526,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5546,12 +5546,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4153</t>
+          <t>4423</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13979</t>
+          <t>13995</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5561,12 +5561,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5581,12 +5581,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8574</t>
+          <t>8674</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20513</t>
+          <t>21670</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2942</t>
+          <t>2517</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5644,7 +5644,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5659,12 +5659,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>757</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7851</t>
+          <t>7537</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5694,12 +5694,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1346</t>
+          <t>1472</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8661</t>
+          <t>8106</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -5742,7 +5742,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3145</t>
+          <t>3118</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5757,7 +5757,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5777,7 +5777,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>3518</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3986</t>
+          <t>4621</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -5967,12 +5967,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>68256</t>
+          <t>68448</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>89390</t>
+          <t>89355</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6002,12 +6002,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>76417</t>
+          <t>76316</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>98138</t>
+          <t>98304</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>57,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>152411</t>
+          <t>151175</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>183729</t>
+          <t>181647</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>54,16%</t>
         </is>
       </c>
     </row>
@@ -6080,12 +6080,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60679</t>
+          <t>59907</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>81614</t>
+          <t>81628</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6095,12 +6095,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>58495</t>
+          <t>60551</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>81982</t>
+          <t>81876</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>125589</t>
+          <t>126989</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>156284</t>
+          <t>156921</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>46,79%</t>
         </is>
       </c>
     </row>
@@ -6193,12 +6193,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7818</t>
+          <t>7460</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19381</t>
+          <t>19833</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6208,12 +6208,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6039</t>
+          <t>6111</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17624</t>
+          <t>17228</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>15895</t>
+          <t>16376</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>31701</t>
+          <t>33289</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,93%</t>
         </is>
       </c>
     </row>
@@ -6311,7 +6311,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4573</t>
+          <t>4571</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>651</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6466</t>
+          <t>7257</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1330</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8644</t>
+          <t>8218</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3144</t>
+          <t>3280</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3527</t>
+          <t>3564</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -6649,12 +6649,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>170396</t>
+          <t>167309</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>200458</t>
+          <t>199040</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6664,12 +6664,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>172603</t>
+          <t>173689</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>205633</t>
+          <t>204028</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>49,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>351422</t>
+          <t>354215</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>396568</t>
+          <t>396015</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>56,99%</t>
         </is>
       </c>
     </row>
@@ -6762,12 +6762,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>124635</t>
+          <t>124693</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>154979</t>
+          <t>155355</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6777,12 +6777,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>119523</t>
+          <t>120053</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>150206</t>
+          <t>150078</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6812,12 +6812,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>252660</t>
+          <t>252944</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>296672</t>
+          <t>293922</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6847,12 +6847,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>42,3%</t>
         </is>
       </c>
     </row>
@@ -6875,12 +6875,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12198</t>
+          <t>12059</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26617</t>
+          <t>25804</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6890,12 +6890,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11923</t>
+          <t>12475</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>25945</t>
+          <t>27389</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6925,12 +6925,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>28212</t>
+          <t>28142</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>49743</t>
+          <t>48056</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -6993,7 +6993,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5066</t>
+          <t>5075</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2183</t>
+          <t>2485</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11320</t>
+          <t>11701</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7038,12 +7038,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3696</t>
+          <t>3904</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13372</t>
+          <t>12958</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7073,12 +7073,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3881</t>
+          <t>4373</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3531</t>
+          <t>3511</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>617</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>6064</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7191,7 +7191,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse bien y en forma en 2023 (tasa de respuesta: 99,83%)</t>
+          <t>Menores según la frecuencia de sentirse bien y en forma en 2023 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7561,12 +7561,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29156</t>
+          <t>28983</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43209</t>
+          <t>42992</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,61%</t>
+          <t>63,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>41250</t>
+          <t>42507</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>59981</t>
+          <t>59498</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7611,12 +7611,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>59,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>76507</t>
+          <t>76467</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>98879</t>
+          <t>98768</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7646,12 +7646,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>59,04%</t>
         </is>
       </c>
     </row>
@@ -7674,12 +7674,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20329</t>
+          <t>20433</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34365</t>
+          <t>34808</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31478</t>
+          <t>31556</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50252</t>
+          <t>48558</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7724,12 +7724,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>48,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>55339</t>
+          <t>56255</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>78308</t>
+          <t>77419</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7759,12 +7759,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>46,28%</t>
         </is>
       </c>
     </row>
@@ -7787,12 +7787,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>1106</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6659</t>
+          <t>7046</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7520</t>
+          <t>7513</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7837,12 +7837,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3320</t>
+          <t>3431</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11724</t>
+          <t>11453</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7872,12 +7872,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -7905,7 +7905,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5978</t>
+          <t>5476</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2196</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10599</t>
+          <t>9722</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7950,12 +7950,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3131</t>
+          <t>3100</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12964</t>
+          <t>13593</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7985,12 +7985,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>8,13%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>73003</t>
+          <t>74301</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>113288</t>
+          <t>114352</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>52,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>80,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>81163</t>
+          <t>81499</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>114721</t>
+          <t>115272</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>66,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>164260</t>
+          <t>163447</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>221366</t>
+          <t>219994</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,01%</t>
+          <t>69,57%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24881</t>
+          <t>22701</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>59346</t>
+          <t>57523</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46822</t>
+          <t>47272</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>76790</t>
+          <t>77481</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>76594</t>
+          <t>78521</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>126482</t>
+          <t>127141</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>40,21%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2868</t>
+          <t>2908</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13136</t>
+          <t>13265</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6003</t>
+          <t>6085</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19656</t>
+          <t>19165</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>10825</t>
+          <t>10471</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>28011</t>
+          <t>28031</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,87%</t>
         </is>
       </c>
     </row>
@@ -8587,7 +8587,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5023</t>
+          <t>4955</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8602,7 +8602,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8617,12 +8617,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1512</t>
+          <t>1385</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9972</t>
+          <t>10039</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8632,12 +8632,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8652,12 +8652,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>2466</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11197</t>
+          <t>11244</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8667,12 +8667,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3683</t>
+          <t>2995</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2659</t>
+          <t>3553</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8785,7 +8785,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>110456</t>
+          <t>108750</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>158813</t>
+          <t>157478</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>129736</t>
+          <t>129412</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>168026</t>
+          <t>167731</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>61,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>248842</t>
+          <t>248949</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>311926</t>
+          <t>316372</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>65,43%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>43558</t>
+          <t>44874</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>85034</t>
+          <t>85644</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>84104</t>
+          <t>84114</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>118807</t>
+          <t>119284</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>141756</t>
+          <t>136815</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>196475</t>
+          <t>196646</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,67%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5174</t>
+          <t>5197</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16490</t>
+          <t>16764</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8757</t>
+          <t>8440</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22131</t>
+          <t>22862</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>16455</t>
+          <t>15996</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>34751</t>
+          <t>34203</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>795</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>7675</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9299,12 +9299,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4877</t>
+          <t>4992</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16559</t>
+          <t>15997</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9314,12 +9314,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9334,12 +9334,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7221</t>
+          <t>6912</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20180</t>
+          <t>19933</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9349,12 +9349,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -9382,7 +9382,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3216</t>
+          <t>4053</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9397,7 +9397,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2827</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9467,7 +9467,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
